--- a/final_project_data/final_project.xlsx
+++ b/final_project_data/final_project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_alldata\Excel\final_project_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B045182-2F7B-4480-81D2-3E9CB882049E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7872AB23-39AF-421D-B7D6-9BF614505EC6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="4" xr2:uid="{D30419F5-293F-444D-A21D-A04983EB7473}"/>
   </bookViews>
@@ -17712,201 +17712,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8DB27C0B-DB5C-4868-96B0-25CF7106F715}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="E4:F8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total_Amount" fld="10" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="12">
-    <chartFormat chart="1" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="1" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{487FA025-94FA-499E-B1CC-9829E848EAAF}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="C4:D10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
@@ -17995,7 +17800,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BE133416-54DF-44A6-B30F-CA07C1FD96D6}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A4:B55" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
@@ -18430,6 +18235,201 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8DB27C0B-DB5C-4868-96B0-25CF7106F715}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="E4:F8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total_Amount" fld="10" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="12">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Region" xr10:uid="{7FC569F8-BB09-4FA8-B52B-09D2CD0BB87A}" sourceName="Region">
   <pivotTables>
@@ -19165,7 +19165,7 @@
       </c>
       <c r="O2" s="11">
         <f ca="1">TODAY()</f>
-        <v>46074</v>
+        <v>46092</v>
       </c>
       <c r="P2" s="26" t="s">
         <v>402</v>
@@ -19462,7 +19462,7 @@
       </c>
       <c r="O6" s="24">
         <f ca="1">NOW()</f>
-        <v>46074.6818375</v>
+        <v>46092.446817592594</v>
       </c>
       <c r="P6" s="30" t="s">
         <v>405</v>
